--- a/data/curated/cristae_automated.xlsx
+++ b/data/curated/cristae_automated.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a57b9f5a08cdd01/Dokumenty/Cristae_článek/GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Nikol/Library/CloudStorage/OneDrive-Osobní/Dokumenty/Cristae_článek/GitHub/curated/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1919" documentId="13_ncr:1_{C5BB00B9-102E-4A48-9846-C49EAE95D290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829BD31A-DDD8-A840-80C2-475FD7CE5702}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65190132-A9F4-CE43-A3E0-F0609DC0407B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25420" windowHeight="19900" activeTab="4" xr2:uid="{5F4DF1EC-AED0-4EA8-89C2-387800CDC649}"/>
+    <workbookView xWindow="5120" yWindow="920" windowWidth="25420" windowHeight="19900" activeTab="10" xr2:uid="{5F4DF1EC-AED0-4EA8-89C2-387800CDC649}"/>
   </bookViews>
   <sheets>
     <sheet name="Ctrl." sheetId="3" r:id="rId1"/>
@@ -463,10 +463,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
   <a:themeElements>
@@ -1964,7 +1960,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B44">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C44"/>
       <c r="D44"/>
@@ -2364,7 +2360,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B61">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C61"/>
       <c r="D61"/>
@@ -6016,7 +6012,7 @@
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B40">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E40">
         <v>11</v>
@@ -6246,7 +6242,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -8486,7 +8482,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B27">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -9223,7 +9219,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -9562,7 +9558,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B35">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D35">
         <v>6</v>
@@ -11370,7 +11366,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E26">
         <v>1</v>
